--- a/inputs/AddictO_Environmental_system_Defs.xlsx
+++ b/inputs/AddictO_Environmental_system_Defs.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00ffe4b5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ebfad0"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1417,7 +1423,6 @@
           <t>A permanent walled and roofed construction.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>human construction</t>
@@ -1428,20 +1433,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>true</t>
@@ -1452,7 +1448,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1463,8 +1458,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1482,7 +1475,6 @@
           <t>A building which is primarily used to facilitate the buying or selling of goods or services.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>building</t>
@@ -1493,20 +1485,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>true</t>
@@ -1517,7 +1500,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1528,8 +1510,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1547,7 +1527,6 @@
           <t>A material entity which has been assembled through the intentional, instinctual, or deliberately programmed efforts of an organism or machine.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>material entity</t>
@@ -1558,24 +1537,16 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>environmental system</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>true</t>
@@ -1586,7 +1557,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1597,8 +1567,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1689,7 +1657,6 @@
           <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>health care facility</t>
@@ -1700,20 +1667,11 @@
           <t>object</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>0</t>
@@ -1724,7 +1682,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>JH; RW</t>
@@ -1735,8 +1692,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1754,7 +1709,6 @@
           <t>A disposition which is realised by an environmental system or system parts thereof.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>disposition</t>
@@ -1765,20 +1719,11 @@
           <t>disposition</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>true</t>
@@ -1789,7 +1734,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1800,8 +1744,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1819,7 +1761,6 @@
           <t>A system which has the disposition to environ one or more material entities.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>system</t>
@@ -1830,8 +1771,6 @@
           <t>System</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>environmental disposition</t>
@@ -1842,16 +1781,11 @@
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>environment</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>true</t>
@@ -1862,7 +1796,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1873,8 +1806,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1892,7 +1823,6 @@
           <t>An architectural structure that bears some function.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>site</t>
@@ -1903,24 +1833,16 @@
           <t>site</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>environmental system</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>true</t>
@@ -1931,7 +1853,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>RW</t>
@@ -1942,8 +1863,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1961,7 +1880,6 @@
           <t>A spatial region whose boundaries are typically defined against some material frame of reference (like the earth).</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>spatial region</t>
@@ -1972,20 +1890,11 @@
           <t>spatial region</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1996,7 +1905,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>RW</t>
@@ -2007,8 +1915,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2026,7 +1932,6 @@
           <t>A geographic region which has causal powers conferred by a legal entity.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>geographic region</t>
@@ -2037,20 +1942,11 @@
           <t>spatial region</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>true</t>
@@ -2061,7 +1957,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>RW</t>
@@ -2072,8 +1967,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2091,7 +1984,6 @@
           <t>A geospatial region that delimits the authority of a formally constituted government to exercise its control within the bounded area.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>geolegal region</t>
@@ -2102,20 +1994,11 @@
           <t>spatial region</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>true</t>
@@ -2126,7 +2009,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>RW</t>
@@ -2137,8 +2019,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2286,7 +2166,6 @@
           <t>A facility that is administered by a health care organization for the purpose of providing health care to a patient or patient population.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>facility</t>
@@ -2297,20 +2176,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>0</t>
@@ -2321,7 +2191,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
           <t>RW; JH</t>
@@ -2332,8 +2201,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2351,7 +2218,6 @@
           <t>A health care facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>health care facility</t>
@@ -2362,20 +2228,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>0</t>
@@ -2386,7 +2243,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>RW; JH</t>
@@ -2397,8 +2253,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2416,7 +2270,6 @@
           <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>hospital facility</t>
@@ -2427,24 +2280,16 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>outpatient clinic</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>0</t>
@@ -2455,7 +2300,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
           <t>RW; JH</t>
@@ -2466,8 +2310,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2485,7 +2327,6 @@
           <t>A construction that has been assembled by deliberate human effort.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>construction</t>
@@ -2496,20 +2337,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>true</t>
@@ -2520,7 +2352,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
           <t>RW</t>
@@ -2531,8 +2362,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2763,7 +2592,6 @@
           <t>A research facility in which systems of manufactured products control internal conditions and in which scientific or technological research, experiments, and measurement may be performed.</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>research facility</t>
@@ -2774,20 +2602,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>0</t>
@@ -2798,7 +2617,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>RW</t>
@@ -2809,8 +2627,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3092,7 +2908,6 @@
           <t>A facility that has at least one housing unit as part in which a person or persons live.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>facility</t>
@@ -3103,20 +2918,11 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>true</t>
@@ -3127,7 +2933,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>RW</t>
@@ -3138,8 +2943,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3157,7 +2960,6 @@
           <t>A commercial building in which a business presents a selection of goods and offers to trade or sell them to customers for money or other goods.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>commercial building</t>
@@ -3168,20 +2970,11 @@
           <t>object</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
@@ -3190,7 +2983,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
           <t>RW</t>
@@ -3201,8 +2993,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3220,7 +3010,6 @@
           <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>immaterial entity</t>
@@ -3231,20 +3020,11 @@
           <t>site</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>true</t>
@@ -3255,7 +3035,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
           <t>RW</t>
@@ -3266,77 +3045,75 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>ADDICTO:0001158</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>social housing</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>A household residence that is provided for people on low incomes or with particular needs by government agencies or non-profit organizations.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>household residence</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Environmental system</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Environmental system</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>https://languages.oup.com/google-dictionary-en/</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>Discussed</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr"/>
-      <c r="W43" s="2" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>Pre-proposed</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3354,7 +3131,6 @@
           <t>A continuant entity that is a continuant_part_of spaceR as defined relative to some frame R</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>immaterial entity</t>
@@ -3365,20 +3141,11 @@
           <t>spatial region</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Environmental system</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>true</t>
@@ -3389,7 +3156,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
           <t>RW</t>
@@ -3400,8 +3166,6 @@
           <t>External</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
